--- a/pfmea_sterile_packaging.xlsx
+++ b/pfmea_sterile_packaging.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1. Scope &amp; Planning" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. Structure Analysis" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. Function Analysis" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. Failure Analysis" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. Risk Rating" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6. Optimization" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. Results Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Scope &amp; Planning" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Structure Analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Function Analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Failure Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Risk Rating" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Optimization" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Results Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -134,7 +134,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -656,7 +656,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 1 – Scope &amp; Planning  |  Sterile Barrier Packaging Seal – Tyvek-Film Pouch (Class III Implants)</t>
+          <t>STEP 1 - Scope &amp; Planning  |  Sterile Barrier Packaging Seal - Tyvek-Film Pouch (Class III Implants)</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Sterile Barrier Packaging Seal – Tyvek-Film Pouch (Class III Implants)</t>
+          <t>Sterile Barrier Packaging Seal - Tyvek-Film Pouch (Class III Implants)</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Class III – PMA support process (21 CFR 814)</t>
+          <t>Class III - PMA support process (21 CFR 814)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Sterile Tyvek-Film Pouch – Primary Sterile Barrier for Class III Implants</t>
+          <t>Sterile Tyvek-Film Pouch - Primary Sterile Barrier for Class III Implants</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>[Your Name] – Manufacturing Transfer Project Engineer</t>
+          <t>[Your Name] - Quality Engineer</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Draft – Internal Review</t>
+          <t>Draft - Internal Review</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 2 – Structure Analysis  |  System Hierarchy Breakdown</t>
+          <t>STEP 2 - Structure Analysis  |  System Hierarchy Breakdown</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Level 1 – System</t>
+          <t>Level 1 - System</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -930,7 +930,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Level 2 – Subsystem</t>
+          <t>Level 2 - Subsystem</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -998,7 +998,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1032,7 +1032,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Level 4 – Interface</t>
+          <t>Level 4 - Interface</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Level 4 – Interface</t>
+          <t>Level 4 - Interface</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1097,7 +1097,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 3 – Function Analysis  |  Intended Functions &amp; Requirements</t>
+          <t>STEP 3 - Function Analysis  |  Intended Functions &amp; Requirements</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>21 CFR 830 UDI; 21 CFR 820.184 DHR; ISO 13485 section 7.5.3 traceability</t>
+          <t>21 CFR 830 UDI; 21 CFR 820.184 DHR; ISO 13485 7.5.3 traceability</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 4 – Failure Analysis  |  Failure Modes, Effects &amp; Causes</t>
+          <t>STEP 4 - Failure Analysis  |  Failure Modes, Effects &amp; Causes</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Visual inspection per WI-VIS-004 – channels &lt; 1 mm not reliably detected visually (GAP)</t>
+          <t>Visual inspection per WI-VIS-004 - channels &lt; 1 mm not reliably detected visually (GAP)</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Bubble emission test samples only (ASTM F2096) – not 100% per lot (DETECTION GAP)</t>
+          <t>Bubble emission test samples only (ASTM F2096) - not 100% per lot (DETECTION GAP)</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Process monitoring via controller display – no independent thermocouple alarm (GAP)</t>
+          <t>Process monitoring via controller display - no independent thermocouple alarm (GAP)</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Peel strength sampled 5 pouches/lot per ASTM F88 – sub-lot variation not captured</t>
+          <t>Peel strength sampled 5 pouches/lot per ASTM F88 - sub-lot variation not captured</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Final QA label review before release – human verification only (GAP)</t>
+          <t>Final QA label review before release - human verification only (GAP)</t>
         </is>
       </c>
     </row>
@@ -1553,9 +1553,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
@@ -1564,14 +1564,14 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AIAG-VDA 2019 Action Priority (AP) -- NOT Traditional RPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="72" customHeight="1">
+          <t>AIAG-VDA 2019 Action Priority (AP) -- NOT Traditional RPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>AIAG-VDA 2019 replaces RPN (S x O x D) with Action Priority (AP: High / Medium / Low). For sterile packaging, the consequence of an undetected seal defect is a non-sterile implant reaching the patient — a catastrophic outcome regardless of defect frequency. ISO 11607 requires validated sterile barrier integrity; AP prioritizes detection gaps accordingly. Any Severity &gt;= 9 failure with Detection &gt;= 7 is automatically High priority — RPN arithmetic can mask this by averaging a low Occurrence score.</t>
+          <t>AIAG-VDA 2019 replaces RPN (SxOxD) with Action Priority (AP: High / Medium / Low). For sterile packaging, the consequence of an undetected seal defect is a non-sterile implant reaching the patient - a catastrophic outcome regardless of defect frequency. ISO 11607 requires validated sterile barrier integrity; AP prioritizes detection gaps accordingly. Any Severity &gt;= 9 failure with Detection &gt;= 7 is automatically High priority - RPN arithmetic can mask this by averaging a low Occurrence score.</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>STEP 5 – Risk Rating  |  AIAG-VDA Action Priority Table</t>
+          <t>STEP 5 - Risk Rating  |  AIAG-VDA Action Priority Table</t>
         </is>
       </c>
     </row>
@@ -1600,19 +1600,19 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>S  (Severity
+          <t>S (Severity
 1-10)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>O  (Occurrence
+          <t>O (Occurrence
 1-10)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D  (Detection
+          <t>D (Detection
 1-10)</t>
         </is>
       </c>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>S&gt;=9 + D&gt;=7: undetected critical failure – patient risk</t>
+          <t>S&gt;=9 + D&gt;=7: undetected critical failure - patient risk</t>
         </is>
       </c>
       <c r="G10" s="19" t="n">
@@ -1851,7 +1851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 6 – Optimization / Corrective Actions  |  Risk Reduction Plan</t>
+          <t>STEP 6 - Optimization / Corrective Actions  |  Risk Reduction Plan</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="75" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
         <is>
           <t>H</t>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Implement 100% bubble emission test per ASTM F2096 (replacing sampling). Add automated peel strength tester with SPC control chart – alert at &lt; 1.8 N/15 mm. Update Control Plan CP-PKG-001 and sampling plan SP-PKG-02. Validate test equipment per IQ/OQ IQ-SIT-001.</t>
+          <t>Implement 100% bubble emission test per ASTM F2096 (replacing sampling). Add automated peel strength tester with SPC control chart - alert at &lt; 1.8 N/15 mm. Update Control Plan CP-PKG-001 and sampling plan SP-PKG-02. Validate test equipment per IQ/OQ IQ-SIT-001.</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="75" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
         <is>
           <t>H</t>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="75" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
           <t>M</t>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="75" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
           <t>M</t>
@@ -2104,14 +2104,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 7 – Results &amp; Documentation Summary</t>
+          <t>STEP 7 - Results &amp; Documentation Summary</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>pFMEA Metrics Summary</t>
+          <t>pFMEA Metrics Summary (auto-computed)</t>
         </is>
       </c>
     </row>
@@ -2148,31 +2148,31 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Medium (M) AP – Initial</t>
+          <t>Medium (M) AP - Initial</t>
         </is>
       </c>
       <c r="D6" s="29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Medium (M) AP – After Actions</t>
+          <t>Medium (M) AP - After Actions</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Low (L) AP – After Actions</t>
+          <t>Low (L) AP - After Actions</t>
         </is>
       </c>
       <c r="D8" s="29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Sterile Packaging – Heat Seal Control Plan</t>
+          <t>Sterile Packaging - Heat Seal Control Plan</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tyvek-Film Pouch Sealing – Setup &amp; Operation</t>
+          <t>Tyvek-Film Pouch Sealing - Setup &amp; Operation</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Seal Integrity Sampling Plan – Bubble Emission &amp; Peel Strength</t>
+          <t>Seal Integrity Sampling Plan - Bubble Emission &amp; Peel Strength</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Heat Sealer Temperature &amp; Dwell Time – Operational Qualification</t>
+          <t>Heat Sealer Temperature &amp; Dwell Time - Operational Qualification</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Process Validation – Sterile Packaging Transfer</t>
+          <t>Process Validation - Sterile Packaging Transfer</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>EtO Sterilization Validation – Class III Implant Family</t>
+          <t>EtO Sterilization Validation - Class III Implant Family</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
